--- a/data/trans_orig/IP3109_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Edad-trans_orig.xlsx
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51877</t>
+          <t>51638</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66253</t>
+          <t>65584</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33338</t>
+          <t>32878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>51790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36119</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22951</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49088</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>71042</t>
+          <t>71182</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>103321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121840</t>
+          <t>122062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110951</t>
+          <t>109862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131728</t>
+          <t>131688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>219010</t>
+          <t>218457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247709</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40248</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58347</t>
+          <t>57829</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>43482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47546</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72842</t>
+          <t>71106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114866</t>
+          <t>114554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134750</t>
+          <t>134869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128589</t>
+          <t>128322</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153917</t>
+          <t>154864</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>249973</t>
+          <t>250034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282272</t>
+          <t>282948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,34 +3283,34 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5095</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>5273</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,03%</t>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17508</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>29782</t>
+          <t>28904</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37229</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39331</t>
+          <t>39899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67517</t>
+          <t>68642</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41925</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76945</t>
+          <t>76932</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>58936</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93973</t>
+          <t>96847</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>109180</t>
+          <t>110190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>161859</t>
+          <t>159154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>153611</t>
+          <t>153841</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>204202</t>
+          <t>201739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>172552</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>212610</t>
+          <t>209907</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>336017</t>
+          <t>334631</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>397953</t>
+          <t>398827</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69808</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126295</t>
+          <t>126640</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>168418</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100778</t>
+          <t>102273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>140992</t>
+          <t>142856</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>127036</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>174211</t>
+          <t>171494</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>239012</t>
+          <t>238246</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>300427</t>
+          <t>301551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>417917</t>
+          <t>415547</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>470550</t>
+          <t>471396</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>453867</t>
+          <t>456600</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>508176</t>
+          <t>509139</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>890806</t>
+          <t>887092</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>967780</t>
+          <t>963706</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6079</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2630</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10743</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4967</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4714</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12218</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8100</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4749</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11899</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24751</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23709</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19317</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>27551</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>63,33%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>73,6%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31052</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>26065</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>35366</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>66,78%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>56,06%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>59202</t>
+          <t>52678</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>45917</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65584</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>164</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,92 +1530,92 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5369</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7508</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2996</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6307</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19169</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13671</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26081</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15905</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10179</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23680</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40306</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51790</t>
+          <t>43734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>28228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>21111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>36915</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>23,51%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>27327</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>20320</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>35919</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31079</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>18983</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>58406</t>
+          <t>53242</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>71182</t>
+          <t>64315</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>104446</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94918</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>113063</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>112668</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>103321</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>122062</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>121159</t>
+          <t>102442</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109862</t>
+          <t>93509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131688</t>
+          <t>110056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>233828</t>
+          <t>206888</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218457</t>
+          <t>194745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245938</t>
+          <t>220021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>181959</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>181959</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>181959</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>533</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,57 +2473,57 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5462</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5411</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5624</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2457</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>27579</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19390</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>36015</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14217</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>9266</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>21767</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45159</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57829</t>
+          <t>53585</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>32024</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23221</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>42355</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>25937</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>18197</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>34311</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43482</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>58697</t>
+          <t>59287</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>72389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133841</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>121170</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145379</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>67,05%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>60,7%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>72,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>125062</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>114554</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>134869</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>66,19%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,93%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>141883</t>
+          <t>124864</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128322</t>
+          <t>113743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154864</t>
+          <t>134449</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>258705</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250034</t>
+          <t>241700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282948</t>
+          <t>273588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>199614</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>199614</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>199614</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>211925</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>211925</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>211925</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>384998</t>
+          <t>374286</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>384998</t>
+          <t>374286</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>384998</t>
+          <t>374286</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>843</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,27 +3180,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2083</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4667</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>350</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>9697</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>16213</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>9841</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>17117</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28662</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>23180</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>16339</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>32914</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>26735</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>17935</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>36204</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38775</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>52499</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39899</t>
+          <t>40629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68642</t>
+          <t>64818</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>74236</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>58930</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>91385</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>25,4%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>59186</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>41845</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>76932</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>21,64%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>75334</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>46787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96847</t>
+          <t>71664</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>134520</t>
+          <t>132154</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110190</t>
+          <t>111640</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>159154</t>
+          <t>154004</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>182534</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>164490</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>200944</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>62,46%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>173357</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>153841</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>201739</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>63,4%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>56,26%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>73,78%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>190985</t>
+          <t>153748</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>169578</t>
+          <t>138616</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>209907</t>
+          <t>167037</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>364342</t>
+          <t>336282</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>334631</t>
+          <t>312443</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>398827</t>
+          <t>357786</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>273443</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>273443</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>273443</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>254463</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>254463</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>254463</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>304999</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>304999</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>304999</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>681</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>546684</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>546684</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>546684</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4013,107 +4013,107 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5589</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>7580</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>6323</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>7825</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>30160</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>33161</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>72427</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>58950</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>85228</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>61570</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>48949</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>76236</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>61717</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>134144</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>117723</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>168418</t>
+          <t>154260</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>142618</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>123591</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>162800</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>120549</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>102273</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>142856</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>117477</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>127036</t>
+          <t>101871</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>135764</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>269546</t>
+          <t>260095</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>238246</t>
+          <t>237508</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>301551</t>
+          <t>290234</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>444531</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>422107</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>466943</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>64,77%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>442139</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>415547</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>471396</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>63,7%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>72,27%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>482179</t>
+          <t>410022</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>456600</t>
+          <t>387816</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>509139</t>
+          <t>429729</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>924319</t>
+          <t>854553</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>887092</t>
+          <t>823894</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>963706</t>
+          <t>882122</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>617334</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>617334</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>617334</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1853</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
